--- a/playernumber.xlsx
+++ b/playernumber.xlsx
@@ -11,7 +11,7 @@
     <sheet name="渠道" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">B服!$A$1:$F$262</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6182,11 +6182,47 @@
       <c r="A243" s="2">
         <v>316</v>
       </c>
+      <c r="B243" s="8">
+        <v>46209</v>
+      </c>
+      <c r="C243" s="8">
+        <v>46217</v>
+      </c>
+      <c r="D243" s="4">
+        <v>138703</v>
+      </c>
+      <c r="E243" s="2">
+        <v>2</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G243" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="2">
         <v>317</v>
       </c>
+      <c r="B244" s="8">
+        <v>46219</v>
+      </c>
+      <c r="C244" s="8">
+        <v>46228</v>
+      </c>
+      <c r="D244" s="4">
+        <v>139947</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G244" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="2">
@@ -6280,7 +6316,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" insertHyperlinks="0" autoFilter="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F241" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F262" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <sortState ref="A2:G193">
@@ -11174,15 +11210,49 @@
       <c r="A204" s="2">
         <v>316</v>
       </c>
-      <c r="F204" s="2"/>
-      <c r="G204" s="2"/>
+      <c r="B204" s="8">
+        <v>46209</v>
+      </c>
+      <c r="C204" s="8">
+        <v>46217</v>
+      </c>
+      <c r="D204" s="3">
+        <v>65267</v>
+      </c>
+      <c r="E204" s="6">
+        <f>D204/B服!D243</f>
+        <v>0.470552187047144</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="2">
         <v>317</v>
       </c>
-      <c r="F205" s="2"/>
-      <c r="G205" s="2"/>
+      <c r="B205" s="8">
+        <v>46219</v>
+      </c>
+      <c r="C205" s="8">
+        <v>46228</v>
+      </c>
+      <c r="D205" s="3">
+        <v>67725</v>
+      </c>
+      <c r="E205" s="6">
+        <f>D205/B服!D244</f>
+        <v>0.4839332032841</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="2">

--- a/playernumber.xlsx
+++ b/playernumber.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6335,8 +6335,8 @@
       <c r="D249" s="4">
         <v>98408</v>
       </c>
-      <c r="E249" s="5" t="s">
-        <v>10</v>
+      <c r="E249" s="5">
+        <v>6</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>7</v>
@@ -6348,6 +6348,24 @@
     <row r="250" spans="1:7">
       <c r="A250" s="5">
         <v>323</v>
+      </c>
+      <c r="B250" s="2">
+        <v>46279</v>
+      </c>
+      <c r="C250" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D250" s="4">
+        <v>42230</v>
+      </c>
+      <c r="E250" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F250" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G250" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -11474,8 +11492,25 @@
       <c r="A211" s="5">
         <v>323</v>
       </c>
-      <c r="F211" s="5"/>
-      <c r="G211" s="5"/>
+      <c r="B211" s="2">
+        <v>46279</v>
+      </c>
+      <c r="C211" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D211" s="3">
+        <v>8356</v>
+      </c>
+      <c r="E211" s="7">
+        <f>D211/B服!D250</f>
+        <v>0.197868813639593</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212" s="5">

--- a/playernumber.xlsx
+++ b/playernumber.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="B服" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="29">
   <si>
     <t>活动编号</t>
   </si>
@@ -6358,8 +6358,8 @@
       <c r="D250" s="4">
         <v>42230</v>
       </c>
-      <c r="E250" s="5" t="s">
-        <v>10</v>
+      <c r="E250" s="5">
+        <v>4</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>12</v>
@@ -6372,10 +6372,46 @@
       <c r="A251" s="5">
         <v>324</v>
       </c>
+      <c r="B251" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C251" s="2">
+        <v>46292</v>
+      </c>
+      <c r="D251" s="4">
+        <v>96188</v>
+      </c>
+      <c r="E251" s="5">
+        <v>4</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G251" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="5">
         <v>325</v>
+      </c>
+      <c r="B252" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C252" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D252" s="4">
+        <v>136279</v>
+      </c>
+      <c r="E252" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F252" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G252" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -11516,15 +11552,49 @@
       <c r="A212" s="5">
         <v>324</v>
       </c>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
+      <c r="B212" s="2">
+        <v>46287</v>
+      </c>
+      <c r="C212" s="2">
+        <v>46292</v>
+      </c>
+      <c r="D212" s="3">
+        <v>37877</v>
+      </c>
+      <c r="E212" s="7">
+        <f>D212/B服!D251</f>
+        <v>0.393780929014014</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" s="5" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="5">
         <v>325</v>
       </c>
-      <c r="F213" s="5"/>
-      <c r="G213" s="5"/>
+      <c r="B213" s="2">
+        <v>46294</v>
+      </c>
+      <c r="C213" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D213" s="3">
+        <v>65023</v>
+      </c>
+      <c r="E213" s="7">
+        <f>D213/B服!D252</f>
+        <v>0.477131472934201</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" s="5">
